--- a/backend/Dataset/sellers.xlsx
+++ b/backend/Dataset/sellers.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universityofexeteruk-my.sharepoint.com/personal/whm208_exeter_ac_uk/Documents/Year 2/COM2020/Coursework 1/Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="227" documentId="8_{F09D7924-9E78-4679-9389-C73088BB3F97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC2D95C0-EE5A-4A49-910E-F51CF2E098E4}"/>
+  <xr:revisionPtr revIDLastSave="295" documentId="8_{F09D7924-9E78-4679-9389-C73088BB3F97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0DDD98C5-D8CA-40A5-BD63-2F7B901A06E2}"/>
   <bookViews>
-    <workbookView xWindow="6750" yWindow="2190" windowWidth="21600" windowHeight="11295" xr2:uid="{D2563AC0-55C2-40AA-9955-193D73686DE6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D2563AC0-55C2-40AA-9955-193D73686DE6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="56">
   <si>
     <t>sellerID</t>
   </si>
@@ -198,6 +198,12 @@
   </si>
   <si>
     <t>Market Place DH1</t>
+  </si>
+  <si>
+    <t>openingTime</t>
+  </si>
+  <si>
+    <t>closingTime</t>
   </si>
 </sst>
 </file>
@@ -256,13 +262,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -601,15 +609,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{181D68F4-F094-4430-BF30-753EE424D58D}">
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.85546875" customWidth="1"/>
     <col min="2" max="2" width="29.28515625" customWidth="1"/>
     <col min="3" max="3" width="54.42578125" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -619,8 +629,14 @@
       <c r="C1" s="3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -630,8 +646,14 @@
       <c r="C2" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2" s="5">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="E2" s="5">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -641,8 +663,14 @@
       <c r="C3" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3" s="5">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -652,8 +680,14 @@
       <c r="C4" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4" s="5">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -663,8 +697,14 @@
       <c r="C5" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D5" s="5">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -674,8 +714,14 @@
       <c r="C6" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D6" s="5">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -685,8 +731,14 @@
       <c r="C7" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D7" s="5">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0.58333333333333337</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -696,8 +748,14 @@
       <c r="C8" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D8" s="5">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -707,8 +765,14 @@
       <c r="C9" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D9" s="5">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0.64583333333333337</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -718,8 +782,14 @@
       <c r="C10" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D10" s="5">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0.64583333333333337</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -729,8 +799,14 @@
       <c r="C11" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D11" s="5">
+        <v>0.3125</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0.8125</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -740,8 +816,14 @@
       <c r="C12" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D12" s="5">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -751,8 +833,14 @@
       <c r="C13" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D13" s="5">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -762,8 +850,14 @@
       <c r="C14" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D14" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0.95833333333333337</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -773,8 +867,14 @@
       <c r="C15" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D15" s="5">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0.70833333333333337</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -784,8 +884,14 @@
       <c r="C16" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D16" s="5">
+        <v>0.375</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -795,8 +901,14 @@
       <c r="C17" s="1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D17" s="5">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -806,8 +918,14 @@
       <c r="C18" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D18" s="5">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="E18" s="5">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -817,8 +935,14 @@
       <c r="C19" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D19" s="5">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="E19" s="5">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -828,8 +952,14 @@
       <c r="C20" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D20" s="5">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="E20" s="5">
+        <v>0.70833333333333337</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -839,8 +969,14 @@
       <c r="C21" s="1" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D21" s="5">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="E21" s="5">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -850,8 +986,14 @@
       <c r="C22" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D22" s="5">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="E22" s="5">
+        <v>0.70833333333333337</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -861,8 +1003,14 @@
       <c r="C23" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D23" s="5">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="E23" s="5">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -872,8 +1020,14 @@
       <c r="C24" s="1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D24" s="5">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="E24" s="5">
+        <v>0.70833333333333337</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -883,8 +1037,14 @@
       <c r="C25" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D25" s="5">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="E25" s="5">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -894,8 +1054,14 @@
       <c r="C26" s="1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D26" s="5">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="E26" s="5">
+        <v>0.70833333333333337</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -905,8 +1071,14 @@
       <c r="C27" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D27" s="5">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="E27" s="5">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -916,8 +1088,14 @@
       <c r="C28" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D28" s="5">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="E28" s="5">
+        <v>0.79166666666666663</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -927,8 +1105,14 @@
       <c r="C29" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D29" s="5">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="E29" s="5">
+        <v>0.79166666666666663</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -938,8 +1122,14 @@
       <c r="C30" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D30" s="5">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="E30" s="5">
+        <v>0.95833333333333337</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -948,6 +1138,12 @@
       </c>
       <c r="C31" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="D31" s="5">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="E31" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/backend/Dataset/sellers.xlsx
+++ b/backend/Dataset/sellers.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universityofexeteruk-my.sharepoint.com/personal/whm208_exeter_ac_uk/Documents/Year 2/COM2020/Coursework 1/Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="295" documentId="8_{F09D7924-9E78-4679-9389-C73088BB3F97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0DDD98C5-D8CA-40A5-BD63-2F7B901A06E2}"/>
+  <xr:revisionPtr revIDLastSave="227" documentId="8_{F09D7924-9E78-4679-9389-C73088BB3F97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC2D95C0-EE5A-4A49-910E-F51CF2E098E4}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D2563AC0-55C2-40AA-9955-193D73686DE6}"/>
+    <workbookView xWindow="6750" yWindow="2190" windowWidth="21600" windowHeight="11295" xr2:uid="{D2563AC0-55C2-40AA-9955-193D73686DE6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="54">
   <si>
     <t>sellerID</t>
   </si>
@@ -198,12 +198,6 @@
   </si>
   <si>
     <t>Market Place DH1</t>
-  </si>
-  <si>
-    <t>openingTime</t>
-  </si>
-  <si>
-    <t>closingTime</t>
   </si>
 </sst>
 </file>
@@ -262,15 +256,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -609,17 +601,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{181D68F4-F094-4430-BF30-753EE424D58D}">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.85546875" customWidth="1"/>
     <col min="2" max="2" width="29.28515625" customWidth="1"/>
     <col min="3" max="3" width="54.42578125" customWidth="1"/>
-    <col min="4" max="4" width="12.85546875" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -629,14 +619,8 @@
       <c r="C1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -646,14 +630,8 @@
       <c r="C2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="5">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="E2" s="5">
-        <v>0.625</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -663,14 +641,8 @@
       <c r="C3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="5">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="E3" s="5">
-        <v>0.625</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -680,14 +652,8 @@
       <c r="C4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="5">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="E4" s="5">
-        <v>0.625</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -697,14 +663,8 @@
       <c r="C5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="5">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="E5" s="5">
-        <v>0.625</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -714,14 +674,8 @@
       <c r="C6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="5">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="E6" s="5">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -731,14 +685,8 @@
       <c r="C7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="5">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="E7" s="5">
-        <v>0.58333333333333337</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -748,14 +696,8 @@
       <c r="C8" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="5">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="E8" s="5">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -765,14 +707,8 @@
       <c r="C9" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="5">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="E9" s="5">
-        <v>0.64583333333333337</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -782,14 +718,8 @@
       <c r="C10" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="5">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="E10" s="5">
-        <v>0.64583333333333337</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -799,14 +729,8 @@
       <c r="C11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="5">
-        <v>0.3125</v>
-      </c>
-      <c r="E11" s="5">
-        <v>0.8125</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -816,14 +740,8 @@
       <c r="C12" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="5">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="E12" s="5">
-        <v>0.625</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -833,14 +751,8 @@
       <c r="C13" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="5">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="E13" s="5">
-        <v>0.875</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -850,14 +762,8 @@
       <c r="C14" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="E14" s="5">
-        <v>0.95833333333333337</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -867,14 +773,8 @@
       <c r="C15" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="5">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="E15" s="5">
-        <v>0.70833333333333337</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -884,14 +784,8 @@
       <c r="C16" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D16" s="5">
-        <v>0.375</v>
-      </c>
-      <c r="E16" s="5">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -901,14 +795,8 @@
       <c r="C17" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D17" s="5">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="E17" s="5">
-        <v>0.83333333333333337</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -918,14 +806,8 @@
       <c r="C18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="5">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="E18" s="5">
-        <v>0.83333333333333337</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -935,14 +817,8 @@
       <c r="C19" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="5">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="E19" s="5">
-        <v>0.83333333333333337</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -952,14 +828,8 @@
       <c r="C20" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D20" s="5">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="E20" s="5">
-        <v>0.70833333333333337</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -969,14 +839,8 @@
       <c r="C21" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D21" s="5">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="E21" s="5">
-        <v>0.83333333333333337</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -986,14 +850,8 @@
       <c r="C22" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D22" s="5">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="E22" s="5">
-        <v>0.70833333333333337</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -1003,14 +861,8 @@
       <c r="C23" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="5">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="E23" s="5">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -1020,14 +872,8 @@
       <c r="C24" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D24" s="5">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="E24" s="5">
-        <v>0.70833333333333337</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -1037,14 +883,8 @@
       <c r="C25" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D25" s="5">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="E25" s="5">
-        <v>0.625</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -1054,14 +894,8 @@
       <c r="C26" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D26" s="5">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="E26" s="5">
-        <v>0.70833333333333337</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -1071,14 +905,8 @@
       <c r="C27" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D27" s="5">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="E27" s="5">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -1088,14 +916,8 @@
       <c r="C28" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D28" s="5">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="E28" s="5">
-        <v>0.79166666666666663</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -1105,14 +927,8 @@
       <c r="C29" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D29" s="5">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="E29" s="5">
-        <v>0.79166666666666663</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -1122,14 +938,8 @@
       <c r="C30" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D30" s="5">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="E30" s="5">
-        <v>0.95833333333333337</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -1138,12 +948,6 @@
       </c>
       <c r="C31" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="D31" s="5">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="E31" s="5">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
